--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_120/per_file_predictions_epoch_120.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_120/per_file_predictions_epoch_120.xlsx
@@ -958,7 +958,7 @@
     <t>0.0063,0.0092,0.9888,0.0010</t>
   </si>
   <si>
-    <t>0.0013,0.8684,0.0007,0.8278</t>
+    <t>0.0013,0.8683,0.0007,0.8278</t>
   </si>
   <si>
     <t>0.0001,0.9999,0.0002,0.0000</t>
@@ -1069,7 +1069,7 @@
     <t>0.0003,0.0008,0.0036,0.9997</t>
   </si>
   <si>
-    <t>0.0002,0.9953,0.8251,0.0001</t>
+    <t>0.0002,0.9953,0.8252,0.0001</t>
   </si>
   <si>
     <t>0.0005,0.7318,0.9822,0.0003</t>
@@ -1198,7 +1198,7 @@
     <t>0.2565,0.6786,0.1089,0.0041</t>
   </si>
   <si>
-    <t>0.1987,0.6959,0.1879,0.0133</t>
+    <t>0.1987,0.6958,0.1879,0.0133</t>
   </si>
   <si>
     <t>0.9879,0.0012,0.0034,0.0004</t>
@@ -1432,7 +1432,7 @@
     <t>0.9578,0.0021,0.0204,0.0008</t>
   </si>
   <si>
-    <t>0.2443,0.0197,0.7218,0.0169</t>
+    <t>0.2443,0.0197,0.7217,0.0169</t>
   </si>
   <si>
     <t>0.2075,0.0018,0.7935,0.0099</t>
@@ -1534,7 +1534,7 @@
     <t>0.9930,0.0019,0.0015,0.0002</t>
   </si>
   <si>
-    <t>0.9822,0.0172,0.0025,0.0004</t>
+    <t>0.9821,0.0172,0.0025,0.0004</t>
   </si>
   <si>
     <t>0.9894,0.0109,0.0013,0.0005</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_120/per_file_predictions_epoch_120.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_120/per_file_predictions_epoch_120.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
   <si>
     <t>Filename</t>
   </si>
@@ -826,16 +826,19 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9497,0.0026,0.0145,0.0057</t>
-  </si>
-  <si>
-    <t>0.0092,0.0010,0.0005,0.9980</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9496,0.0026,0.0146,0.0057</t>
+  </si>
+  <si>
+    <t>0.0091,0.0010,0.0005,0.9980</t>
   </si>
   <si>
     <t>0.9698,0.0009,0.0003,0.0097</t>
   </si>
   <si>
-    <t>0.2253,0.0007,0.0023,0.8837</t>
+    <t>0.2250,0.0007,0.0023,0.8838</t>
   </si>
   <si>
     <t>0.9949,0.0015,0.0012,0.0002</t>
@@ -847,13 +850,13 @@
     <t>0.9909,0.0025,0.0026,0.0002</t>
   </si>
   <si>
-    <t>0.9949,0.0016,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9753,0.0359,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9897,0.0091,0.0015,0.0005</t>
+    <t>0.9948,0.0016,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9752,0.0359,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9897,0.0091,0.0015,0.0006</t>
   </si>
   <si>
     <t>0.9960,0.0015,0.0007,0.0001</t>
@@ -862,19 +865,19 @@
     <t>0.9942,0.0019,0.0013,0.0002</t>
   </si>
   <si>
-    <t>0.7629,0.0051,0.2248,0.0030</t>
+    <t>0.7621,0.0051,0.2258,0.0030</t>
   </si>
   <si>
     <t>0.0159,0.0126,0.9798,0.0019</t>
   </si>
   <si>
-    <t>0.2998,0.0007,0.8173,0.0002</t>
-  </si>
-  <si>
-    <t>0.0551,0.0035,0.9541,0.0018</t>
-  </si>
-  <si>
-    <t>0.6545,0.0006,0.4458,0.0003</t>
+    <t>0.2994,0.0007,0.8177,0.0002</t>
+  </si>
+  <si>
+    <t>0.0550,0.0035,0.9541,0.0018</t>
+  </si>
+  <si>
+    <t>0.6535,0.0006,0.4471,0.0003</t>
   </si>
   <si>
     <t>0.0010,0.9986,0.0069,0.0010</t>
@@ -892,28 +895,28 @@
     <t>0.0010,0.9992,0.0066,0.0002</t>
   </si>
   <si>
-    <t>0.3723,0.0011,0.6759,0.0018</t>
-  </si>
-  <si>
-    <t>0.0714,0.0137,0.9043,0.0062</t>
+    <t>0.3713,0.0011,0.6769,0.0018</t>
+  </si>
+  <si>
+    <t>0.0712,0.0137,0.9046,0.0062</t>
   </si>
   <si>
     <t>0.0200,0.0003,0.9888,0.0002</t>
   </si>
   <si>
-    <t>0.0233,0.0018,0.9820,0.0013</t>
+    <t>0.0232,0.0018,0.9820,0.0013</t>
   </si>
   <si>
     <t>0.0155,0.0008,0.9898,0.0008</t>
   </si>
   <si>
-    <t>0.0418,0.0002,0.9767,0.0003</t>
+    <t>0.0418,0.0002,0.9768,0.0003</t>
   </si>
   <si>
     <t>0.0089,0.0002,0.9948,0.0003</t>
   </si>
   <si>
-    <t>0.6657,0.2892,0.0342,0.0025</t>
+    <t>0.6655,0.2891,0.0344,0.0025</t>
   </si>
   <si>
     <t>0.9596,0.0501,0.0021,0.0006</t>
@@ -922,49 +925,49 @@
     <t>0.0021,0.0008,0.9986,0.0003</t>
   </si>
   <si>
-    <t>0.0184,0.1041,0.9056,0.0011</t>
-  </si>
-  <si>
-    <t>0.9628,0.0057,0.0139,0.0007</t>
-  </si>
-  <si>
-    <t>0.9324,0.0255,0.0221,0.0009</t>
-  </si>
-  <si>
-    <t>0.4271,0.6630,0.0217,0.0025</t>
-  </si>
-  <si>
-    <t>0.0046,0.9469,0.6565,0.0013</t>
-  </si>
-  <si>
-    <t>0.0004,0.6351,0.9891,0.0001</t>
+    <t>0.0184,0.1039,0.9057,0.0011</t>
+  </si>
+  <si>
+    <t>0.9626,0.0057,0.0140,0.0007</t>
+  </si>
+  <si>
+    <t>0.9322,0.0254,0.0222,0.0009</t>
+  </si>
+  <si>
+    <t>0.4271,0.6628,0.0218,0.0025</t>
+  </si>
+  <si>
+    <t>0.0046,0.9468,0.6570,0.0013</t>
+  </si>
+  <si>
+    <t>0.0004,0.6347,0.9891,0.0001</t>
   </si>
   <si>
     <t>0.0040,0.0019,0.9954,0.0006</t>
   </si>
   <si>
-    <t>0.0421,0.0224,0.9279,0.0027</t>
-  </si>
-  <si>
-    <t>0.0697,0.0015,0.9316,0.0076</t>
-  </si>
-  <si>
-    <t>0.0010,0.3557,0.9838,0.0004</t>
-  </si>
-  <si>
-    <t>0.0045,0.9938,0.0091,0.0003</t>
+    <t>0.0420,0.0224,0.9280,0.0027</t>
+  </si>
+  <si>
+    <t>0.0695,0.0015,0.9319,0.0076</t>
+  </si>
+  <si>
+    <t>0.0010,0.3552,0.9838,0.0004</t>
+  </si>
+  <si>
+    <t>0.0045,0.9938,0.0092,0.0003</t>
   </si>
   <si>
     <t>0.0063,0.0092,0.9888,0.0010</t>
   </si>
   <si>
-    <t>0.0013,0.8683,0.0007,0.8278</t>
+    <t>0.0013,0.8684,0.0007,0.8278</t>
   </si>
   <si>
     <t>0.0001,0.9999,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.0003,0.9995,0.0327,0.0002</t>
+    <t>0.0003,0.9995,0.0329,0.0002</t>
   </si>
   <si>
     <t>0.0001,0.9999,0.0071,0.0001</t>
@@ -973,43 +976,43 @@
     <t>0.0002,0.0101,0.9990,0.0002</t>
   </si>
   <si>
-    <t>0.0013,0.2912,0.9816,0.0014</t>
+    <t>0.0013,0.2910,0.9816,0.0014</t>
   </si>
   <si>
     <t>0.0085,0.0013,0.9916,0.0013</t>
   </si>
   <si>
-    <t>0.0296,0.0001,0.9901,0.0001</t>
-  </si>
-  <si>
-    <t>0.0136,0.0017,0.9897,0.0005</t>
+    <t>0.0295,0.0001,0.9902,0.0001</t>
+  </si>
+  <si>
+    <t>0.0135,0.0017,0.9897,0.0005</t>
   </si>
   <si>
     <t>0.0187,0.0184,0.9582,0.0037</t>
   </si>
   <si>
-    <t>0.9668,0.0146,0.0119,0.0008</t>
-  </si>
-  <si>
-    <t>0.9790,0.0011,0.0134,0.0002</t>
-  </si>
-  <si>
-    <t>0.9721,0.0127,0.0081,0.0039</t>
-  </si>
-  <si>
-    <t>0.2223,0.0020,0.8367,0.0008</t>
+    <t>0.9666,0.0146,0.0120,0.0008</t>
+  </si>
+  <si>
+    <t>0.9788,0.0011,0.0135,0.0002</t>
+  </si>
+  <si>
+    <t>0.9720,0.0127,0.0082,0.0039</t>
+  </si>
+  <si>
+    <t>0.2215,0.0020,0.8376,0.0008</t>
   </si>
   <si>
     <t>0.9885,0.0008,0.0053,0.0001</t>
   </si>
   <si>
-    <t>0.9914,0.0017,0.0031,0.0004</t>
-  </si>
-  <si>
-    <t>0.9913,0.0017,0.0029,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9966,0.8414,0.0001</t>
+    <t>0.9913,0.0017,0.0031,0.0004</t>
+  </si>
+  <si>
+    <t>0.9912,0.0017,0.0029,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9966,0.8417,0.0001</t>
   </si>
   <si>
     <t>0.0005,0.0338,0.9983,0.0001</t>
@@ -1018,7 +1021,7 @@
     <t>0.0021,0.0110,0.9943,0.0008</t>
   </si>
   <si>
-    <t>0.0003,0.9852,0.8125,0.0004</t>
+    <t>0.0003,0.9852,0.8131,0.0004</t>
   </si>
   <si>
     <t>0.0001,0.0001,0.9999,0.0001</t>
@@ -1030,22 +1033,22 @@
     <t>0.0005,0.9996,0.0013,0.0000</t>
   </si>
   <si>
-    <t>0.9583,0.0006,0.0344,0.0001</t>
-  </si>
-  <si>
-    <t>0.1516,0.0621,0.8128,0.0045</t>
+    <t>0.9582,0.0006,0.0346,0.0001</t>
+  </si>
+  <si>
+    <t>0.1511,0.0620,0.8134,0.0045</t>
   </si>
   <si>
     <t>0.0213,0.0092,0.9832,0.0015</t>
   </si>
   <si>
-    <t>0.0007,0.9584,0.8835,0.0006</t>
-  </si>
-  <si>
-    <t>0.0005,0.8553,0.9709,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0924,0.0000</t>
+    <t>0.0007,0.9584,0.8837,0.0006</t>
+  </si>
+  <si>
+    <t>0.0005,0.8551,0.9709,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0926,0.0000</t>
   </si>
   <si>
     <t>0.0004,0.9388,0.9409,0.0006</t>
@@ -1063,28 +1066,28 @@
     <t>0.0042,0.0003,0.0027,0.9984</t>
   </si>
   <si>
-    <t>0.0174,0.0022,0.0032,0.9933</t>
+    <t>0.0174,0.0022,0.0033,0.9933</t>
   </si>
   <si>
     <t>0.0003,0.0008,0.0036,0.9997</t>
   </si>
   <si>
-    <t>0.0002,0.9953,0.8252,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.7318,0.9822,0.0003</t>
-  </si>
-  <si>
-    <t>0.0020,0.9695,0.4595,0.0008</t>
-  </si>
-  <si>
-    <t>0.0005,0.7808,0.9825,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9929,0.9189,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9961,0.2818,0.0002</t>
+    <t>0.0002,0.9952,0.8257,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.7314,0.9822,0.0003</t>
+  </si>
+  <si>
+    <t>0.0020,0.9694,0.4605,0.0008</t>
+  </si>
+  <si>
+    <t>0.0005,0.7806,0.9825,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9929,0.9190,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9961,0.2825,0.0002</t>
   </si>
   <si>
     <t>0.9942,0.0067,0.0005,0.0002</t>
@@ -1114,16 +1117,16 @@
     <t>0.9935,0.0012,0.0019,0.0003</t>
   </si>
   <si>
-    <t>0.9912,0.0074,0.0015,0.0005</t>
-  </si>
-  <si>
-    <t>0.9969,0.0017,0.0004,0.0001</t>
+    <t>0.9912,0.0075,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.9968,0.0017,0.0004,0.0001</t>
   </si>
   <si>
     <t>0.9955,0.0025,0.0006,0.0003</t>
   </si>
   <si>
-    <t>0.9909,0.0064,0.0013,0.0007</t>
+    <t>0.9908,0.0064,0.0013,0.0007</t>
   </si>
   <si>
     <t>0.9970,0.0020,0.0004,0.0004</t>
@@ -1138,22 +1141,22 @@
     <t>0.0022,0.0001,0.9989,0.0001</t>
   </si>
   <si>
-    <t>0.0261,0.0032,0.9776,0.0018</t>
-  </si>
-  <si>
-    <t>0.9721,0.0001,0.0316,0.0002</t>
-  </si>
-  <si>
-    <t>0.0522,0.0028,0.9493,0.0012</t>
+    <t>0.0261,0.0031,0.9777,0.0018</t>
+  </si>
+  <si>
+    <t>0.9720,0.0001,0.0318,0.0002</t>
+  </si>
+  <si>
+    <t>0.0521,0.0028,0.9495,0.0012</t>
   </si>
   <si>
     <t>0.0002,0.9999,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.4167,0.6883,0.0027,0.0008</t>
-  </si>
-  <si>
-    <t>0.0876,0.9286,0.0427,0.0069</t>
+    <t>0.4168,0.6883,0.0027,0.0008</t>
+  </si>
+  <si>
+    <t>0.0876,0.9285,0.0429,0.0069</t>
   </si>
   <si>
     <t>0.0002,0.9999,0.0003,0.0000</t>
@@ -1162,61 +1165,61 @@
     <t>0.0000,1.0000,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.6911,0.3250,0.0459,0.0030</t>
-  </si>
-  <si>
-    <t>0.1658,0.0274,0.8245,0.0095</t>
-  </si>
-  <si>
-    <t>0.0485,0.0078,0.9482,0.0042</t>
-  </si>
-  <si>
-    <t>0.2870,0.0071,0.7006,0.0032</t>
-  </si>
-  <si>
-    <t>0.1304,0.0144,0.8674,0.0096</t>
-  </si>
-  <si>
-    <t>0.0004,0.6330,0.5761,0.1953</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0013,0.0000</t>
+    <t>0.6909,0.3249,0.0462,0.0030</t>
+  </si>
+  <si>
+    <t>0.1652,0.0273,0.8253,0.0095</t>
+  </si>
+  <si>
+    <t>0.0484,0.0078,0.9483,0.0042</t>
+  </si>
+  <si>
+    <t>0.2863,0.0071,0.7015,0.0032</t>
+  </si>
+  <si>
+    <t>0.1299,0.0144,0.8678,0.0096</t>
+  </si>
+  <si>
+    <t>0.0004,0.6326,0.5767,0.1949</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0014,0.0000</t>
   </si>
   <si>
     <t>0.0001,0.9999,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.9994,0.0003,0.0031</t>
-  </si>
-  <si>
-    <t>0.0003,0.9990,0.0451,0.0003</t>
-  </si>
-  <si>
-    <t>0.0027,0.9887,0.3136,0.0010</t>
-  </si>
-  <si>
-    <t>0.2565,0.6786,0.1089,0.0041</t>
-  </si>
-  <si>
-    <t>0.1987,0.6958,0.1879,0.0133</t>
+    <t>0.0002,0.9994,0.0004,0.0031</t>
+  </si>
+  <si>
+    <t>0.0003,0.9990,0.0452,0.0003</t>
+  </si>
+  <si>
+    <t>0.0027,0.9887,0.3143,0.0010</t>
+  </si>
+  <si>
+    <t>0.2562,0.6779,0.1095,0.0041</t>
+  </si>
+  <si>
+    <t>0.1986,0.6953,0.1886,0.0133</t>
   </si>
   <si>
     <t>0.9879,0.0012,0.0034,0.0004</t>
   </si>
   <si>
-    <t>0.9942,0.0042,0.0004,0.0004</t>
+    <t>0.9941,0.0042,0.0004,0.0004</t>
   </si>
   <si>
     <t>0.9921,0.0045,0.0012,0.0006</t>
   </si>
   <si>
-    <t>0.9907,0.0016,0.0030,0.0005</t>
+    <t>0.9907,0.0017,0.0030,0.0005</t>
   </si>
   <si>
     <t>0.9927,0.0038,0.0013,0.0011</t>
   </si>
   <si>
-    <t>0.9821,0.0013,0.0065,0.0004</t>
+    <t>0.9820,0.0013,0.0065,0.0004</t>
   </si>
   <si>
     <t>0.9955,0.0013,0.0009,0.0002</t>
@@ -1225,10 +1228,10 @@
     <t>0.9954,0.0009,0.0011,0.0002</t>
   </si>
   <si>
-    <t>0.0011,0.7860,0.9647,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.4989,0.9909,0.0001</t>
+    <t>0.0011,0.7854,0.9648,0.0005</t>
+  </si>
+  <si>
+    <t>0.0005,0.4987,0.9909,0.0001</t>
   </si>
   <si>
     <t>0.0007,0.0332,0.9969,0.0003</t>
@@ -1237,16 +1240,16 @@
     <t>0.0102,0.0067,0.9904,0.0003</t>
   </si>
   <si>
-    <t>0.9541,0.0011,0.0273,0.0010</t>
-  </si>
-  <si>
-    <t>0.3459,0.4341,0.0585,0.0060</t>
-  </si>
-  <si>
-    <t>0.2002,0.0002,0.8776,0.0010</t>
-  </si>
-  <si>
-    <t>0.4916,0.0072,0.4766,0.0058</t>
+    <t>0.9540,0.0011,0.0274,0.0010</t>
+  </si>
+  <si>
+    <t>0.3458,0.4334,0.0588,0.0060</t>
+  </si>
+  <si>
+    <t>0.1995,0.0002,0.8781,0.0010</t>
+  </si>
+  <si>
+    <t>0.4900,0.0071,0.4783,0.0058</t>
   </si>
   <si>
     <t>0.0283,0.0001,0.0013,0.9924</t>
@@ -1255,25 +1258,25 @@
     <t>0.0000,0.0006,0.0006,1.0000</t>
   </si>
   <si>
-    <t>0.0001,0.0003,0.0006,1.0000</t>
+    <t>0.0001,0.0004,0.0006,1.0000</t>
   </si>
   <si>
     <t>0.0068,0.0003,0.0019,0.9985</t>
   </si>
   <si>
-    <t>0.0002,0.9931,0.7928,0.0002</t>
-  </si>
-  <si>
-    <t>0.9889,0.0016,0.0036,0.0003</t>
-  </si>
-  <si>
-    <t>0.0133,0.9845,0.0176,0.0085</t>
+    <t>0.0002,0.9931,0.7932,0.0002</t>
+  </si>
+  <si>
+    <t>0.9888,0.0016,0.0037,0.0003</t>
+  </si>
+  <si>
+    <t>0.0133,0.9844,0.0177,0.0085</t>
   </si>
   <si>
     <t>0.9938,0.0009,0.0018,0.0001</t>
   </si>
   <si>
-    <t>0.0305,0.9785,0.0124,0.0013</t>
+    <t>0.0305,0.9784,0.0125,0.0013</t>
   </si>
   <si>
     <t>0.9943,0.0008,0.0010,0.0006</t>
@@ -1282,43 +1285,43 @@
     <t>0.0044,0.0000,0.9990,0.0000</t>
   </si>
   <si>
-    <t>0.0366,0.0000,0.9898,0.0000</t>
+    <t>0.0365,0.0000,0.9899,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.8331,0.0000,0.0796,0.0012</t>
+    <t>0.8323,0.0000,0.0802,0.0012</t>
   </si>
   <si>
     <t>0.9894,0.0028,0.0023,0.0002</t>
   </si>
   <si>
-    <t>0.7321,0.1488,0.0521,0.0016</t>
-  </si>
-  <si>
-    <t>0.9881,0.0021,0.0039,0.0004</t>
-  </si>
-  <si>
-    <t>0.9484,0.0277,0.0134,0.0011</t>
-  </si>
-  <si>
-    <t>0.0636,0.9355,0.0219,0.0073</t>
-  </si>
-  <si>
-    <t>0.8754,0.0585,0.0537,0.0023</t>
-  </si>
-  <si>
-    <t>0.7762,0.0181,0.1526,0.0021</t>
+    <t>0.7321,0.1486,0.0523,0.0016</t>
+  </si>
+  <si>
+    <t>0.9880,0.0021,0.0039,0.0004</t>
+  </si>
+  <si>
+    <t>0.9483,0.0278,0.0134,0.0011</t>
+  </si>
+  <si>
+    <t>0.0637,0.9353,0.0220,0.0073</t>
+  </si>
+  <si>
+    <t>0.8750,0.0585,0.0540,0.0023</t>
+  </si>
+  <si>
+    <t>0.7754,0.0181,0.1534,0.0021</t>
   </si>
   <si>
     <t>0.9921,0.0055,0.0012,0.0003</t>
   </si>
   <si>
-    <t>0.9936,0.0054,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9853,0.0030,0.0055,0.0007</t>
+    <t>0.9935,0.0055,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9852,0.0030,0.0055,0.0007</t>
   </si>
   <si>
     <t>0.9924,0.0012,0.0022,0.0002</t>
@@ -1330,46 +1333,46 @@
     <t>0.9906,0.0061,0.0017,0.0005</t>
   </si>
   <si>
-    <t>0.9892,0.0043,0.0025,0.0004</t>
+    <t>0.9891,0.0043,0.0025,0.0004</t>
   </si>
   <si>
     <t>0.9943,0.0017,0.0012,0.0002</t>
   </si>
   <si>
-    <t>0.7926,0.2316,0.0101,0.0042</t>
-  </si>
-  <si>
-    <t>0.2384,0.8128,0.0183,0.0047</t>
-  </si>
-  <si>
-    <t>0.7554,0.3195,0.0016,0.0004</t>
-  </si>
-  <si>
-    <t>0.9129,0.0134,0.0601,0.0011</t>
+    <t>0.7921,0.2321,0.0102,0.0042</t>
+  </si>
+  <si>
+    <t>0.2383,0.8128,0.0184,0.0048</t>
+  </si>
+  <si>
+    <t>0.7552,0.3198,0.0016,0.0004</t>
+  </si>
+  <si>
+    <t>0.9125,0.0134,0.0605,0.0011</t>
   </si>
   <si>
     <t>0.9906,0.0061,0.0018,0.0002</t>
   </si>
   <si>
-    <t>0.8725,0.0345,0.0704,0.0020</t>
-  </si>
-  <si>
-    <t>0.9891,0.0019,0.0041,0.0002</t>
-  </si>
-  <si>
-    <t>0.9246,0.0684,0.0204,0.0037</t>
+    <t>0.8721,0.0345,0.0708,0.0020</t>
+  </si>
+  <si>
+    <t>0.9891,0.0019,0.0042,0.0002</t>
+  </si>
+  <si>
+    <t>0.9244,0.0686,0.0205,0.0037</t>
   </si>
   <si>
     <t>0.0093,0.0067,0.9950,0.0004</t>
   </si>
   <si>
-    <t>0.8610,0.0613,0.0609,0.0016</t>
+    <t>0.8607,0.0613,0.0612,0.0016</t>
   </si>
   <si>
     <t>0.0014,0.0005,0.9990,0.0001</t>
   </si>
   <si>
-    <t>0.0002,0.1394,0.9958,0.0005</t>
+    <t>0.0002,0.1393,0.9958,0.0005</t>
   </si>
   <si>
     <t>0.0101,0.0024,0.9926,0.0013</t>
@@ -1387,88 +1390,88 @@
     <t>0.0216,0.0014,0.9832,0.0007</t>
   </si>
   <si>
-    <t>0.1446,0.0046,0.8614,0.0021</t>
-  </si>
-  <si>
-    <t>0.2447,0.0003,0.8471,0.0002</t>
-  </si>
-  <si>
-    <t>0.4841,0.0211,0.4458,0.0058</t>
-  </si>
-  <si>
-    <t>0.0475,0.0093,0.9487,0.0029</t>
-  </si>
-  <si>
-    <t>0.0168,0.0208,0.9667,0.0007</t>
-  </si>
-  <si>
-    <t>0.0785,0.0024,0.9400,0.0010</t>
-  </si>
-  <si>
-    <t>0.1079,0.0056,0.8994,0.0043</t>
-  </si>
-  <si>
-    <t>0.5369,0.0237,0.3774,0.0041</t>
-  </si>
-  <si>
-    <t>0.0769,0.9643,0.0052,0.0002</t>
+    <t>0.1441,0.0046,0.8619,0.0021</t>
+  </si>
+  <si>
+    <t>0.2443,0.0003,0.8474,0.0002</t>
+  </si>
+  <si>
+    <t>0.4830,0.0211,0.4472,0.0058</t>
+  </si>
+  <si>
+    <t>0.0474,0.0093,0.9488,0.0029</t>
+  </si>
+  <si>
+    <t>0.0168,0.0208,0.9668,0.0007</t>
+  </si>
+  <si>
+    <t>0.0783,0.0024,0.9401,0.0010</t>
+  </si>
+  <si>
+    <t>0.1077,0.0056,0.8996,0.0043</t>
+  </si>
+  <si>
+    <t>0.5357,0.0237,0.3788,0.0041</t>
+  </si>
+  <si>
+    <t>0.0767,0.9644,0.0052,0.0002</t>
   </si>
   <si>
     <t>0.0080,0.9961,0.0014,0.0002</t>
   </si>
   <si>
-    <t>0.1545,0.9174,0.0033,0.0005</t>
-  </si>
-  <si>
-    <t>0.9793,0.0175,0.0031,0.0002</t>
-  </si>
-  <si>
-    <t>0.7328,0.3878,0.0047,0.0005</t>
-  </si>
-  <si>
-    <t>0.1776,0.8207,0.0169,0.0017</t>
-  </si>
-  <si>
-    <t>0.9578,0.0021,0.0204,0.0008</t>
-  </si>
-  <si>
-    <t>0.2443,0.0197,0.7217,0.0169</t>
-  </si>
-  <si>
-    <t>0.2075,0.0018,0.7935,0.0099</t>
-  </si>
-  <si>
-    <t>0.5877,0.0146,0.3099,0.0032</t>
+    <t>0.1546,0.9174,0.0033,0.0005</t>
+  </si>
+  <si>
+    <t>0.9792,0.0176,0.0031,0.0002</t>
+  </si>
+  <si>
+    <t>0.7323,0.3884,0.0047,0.0005</t>
+  </si>
+  <si>
+    <t>0.1775,0.8206,0.0170,0.0017</t>
+  </si>
+  <si>
+    <t>0.9576,0.0021,0.0206,0.0008</t>
+  </si>
+  <si>
+    <t>0.2434,0.0196,0.7229,0.0168</t>
+  </si>
+  <si>
+    <t>0.2070,0.0018,0.7940,0.0099</t>
+  </si>
+  <si>
+    <t>0.5864,0.0145,0.3113,0.0032</t>
   </si>
   <si>
     <t>0.0089,0.0006,0.9936,0.0005</t>
   </si>
   <si>
-    <t>0.0902,0.0061,0.9330,0.0017</t>
-  </si>
-  <si>
-    <t>0.0400,0.0511,0.9100,0.0009</t>
+    <t>0.0898,0.0061,0.9334,0.0017</t>
+  </si>
+  <si>
+    <t>0.0398,0.0509,0.9105,0.0009</t>
   </si>
   <si>
     <t>0.0080,0.0027,0.9921,0.0004</t>
   </si>
   <si>
-    <t>0.0248,0.0157,0.9614,0.0003</t>
+    <t>0.0247,0.0157,0.9616,0.0003</t>
   </si>
   <si>
     <t>0.9919,0.0014,0.0023,0.0001</t>
   </si>
   <si>
-    <t>0.9709,0.0193,0.0069,0.0012</t>
-  </si>
-  <si>
-    <t>0.9403,0.0558,0.0068,0.0025</t>
+    <t>0.9709,0.0194,0.0069,0.0012</t>
+  </si>
+  <si>
+    <t>0.9402,0.0560,0.0068,0.0025</t>
   </si>
   <si>
     <t>0.9895,0.0121,0.0010,0.0005</t>
   </si>
   <si>
-    <t>0.9599,0.0327,0.0092,0.0021</t>
+    <t>0.9598,0.0327,0.0093,0.0021</t>
   </si>
   <si>
     <t>0.9767,0.0231,0.0034,0.0009</t>
@@ -1477,16 +1480,16 @@
     <t>0.9794,0.0120,0.0050,0.0012</t>
   </si>
   <si>
-    <t>0.9891,0.0018,0.0038,0.0002</t>
-  </si>
-  <si>
-    <t>0.0161,0.0028,0.9907,0.0010</t>
-  </si>
-  <si>
-    <t>0.1331,0.0367,0.8559,0.0026</t>
-  </si>
-  <si>
-    <t>0.5501,0.0089,0.4453,0.0070</t>
+    <t>0.9890,0.0018,0.0038,0.0002</t>
+  </si>
+  <si>
+    <t>0.0160,0.0028,0.9908,0.0010</t>
+  </si>
+  <si>
+    <t>0.1326,0.0365,0.8567,0.0026</t>
+  </si>
+  <si>
+    <t>0.5481,0.0089,0.4479,0.0070</t>
   </si>
   <si>
     <t>0.0011,0.0003,0.9990,0.0001</t>
@@ -1495,40 +1498,40 @@
     <t>0.0003,0.0022,0.9993,0.0002</t>
   </si>
   <si>
-    <t>0.0073,0.0408,0.9726,0.0016</t>
+    <t>0.0073,0.0407,0.9726,0.0016</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0366,0.0095,0.9577,0.0014</t>
+    <t>0.0366,0.0095,0.9578,0.0014</t>
   </si>
   <si>
     <t>0.0045,0.0030,0.9945,0.0005</t>
   </si>
   <si>
-    <t>0.0473,0.0181,0.9374,0.0054</t>
-  </si>
-  <si>
-    <t>0.8087,0.0008,0.1979,0.0016</t>
-  </si>
-  <si>
-    <t>0.3531,0.0008,0.6306,0.0054</t>
-  </si>
-  <si>
-    <t>0.9647,0.0069,0.0130,0.0007</t>
+    <t>0.0472,0.0181,0.9375,0.0053</t>
+  </si>
+  <si>
+    <t>0.8082,0.0008,0.1985,0.0016</t>
+  </si>
+  <si>
+    <t>0.3522,0.0008,0.6316,0.0053</t>
+  </si>
+  <si>
+    <t>0.9646,0.0069,0.0131,0.0007</t>
   </si>
   <si>
     <t>0.9942,0.0041,0.0007,0.0001</t>
   </si>
   <si>
-    <t>0.9849,0.0184,0.0012,0.0005</t>
+    <t>0.9849,0.0185,0.0013,0.0005</t>
   </si>
   <si>
     <t>0.9917,0.0053,0.0014,0.0002</t>
   </si>
   <si>
-    <t>0.9389,0.0571,0.0072,0.0010</t>
+    <t>0.9388,0.0572,0.0072,0.0010</t>
   </si>
   <si>
     <t>0.9930,0.0019,0.0015,0.0002</t>
@@ -1552,37 +1555,37 @@
     <t>0.0025,0.0042,0.9970,0.0002</t>
   </si>
   <si>
-    <t>0.0351,0.0341,0.9090,0.0017</t>
+    <t>0.0350,0.0341,0.9091,0.0017</t>
   </si>
   <si>
     <t>0.0281,0.0009,0.9819,0.0004</t>
   </si>
   <si>
-    <t>0.7669,0.0325,0.0551,0.0134</t>
-  </si>
-  <si>
-    <t>0.1279,0.0251,0.7939,0.0070</t>
+    <t>0.7660,0.0325,0.0555,0.0134</t>
+  </si>
+  <si>
+    <t>0.1274,0.0250,0.7948,0.0070</t>
   </si>
   <si>
     <t>0.0045,0.0008,0.9960,0.0008</t>
   </si>
   <si>
-    <t>0.9430,0.0003,0.0073,0.0101</t>
+    <t>0.9427,0.0003,0.0074,0.0101</t>
   </si>
   <si>
     <t>0.0012,0.0026,0.0003,0.9996</t>
   </si>
   <si>
-    <t>0.0046,0.0006,0.0113,0.9973</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0610,0.9997</t>
+    <t>0.0046,0.0006,0.0114,0.9973</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.0611,0.9997</t>
   </si>
   <si>
     <t>0.0002,0.0005,0.0029,0.9999</t>
   </si>
   <si>
-    <t>0.8291,0.0041,0.0181,0.1107</t>
+    <t>0.8289,0.0041,0.0181,0.1107</t>
   </si>
 </sst>
 </file>
@@ -1968,7 +1971,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1982,7 +1985,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1996,7 +1999,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2010,7 +2013,7 @@
         <v>265</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2024,7 +2027,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2038,7 +2041,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2052,7 +2055,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2066,7 +2069,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2080,7 +2083,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2094,7 +2097,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2108,7 +2111,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2122,7 +2125,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2136,7 +2139,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2150,7 +2153,7 @@
         <v>266</v>
       </c>
       <c r="D15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2164,7 +2167,7 @@
         <v>266</v>
       </c>
       <c r="D16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2178,7 +2181,7 @@
         <v>266</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2192,7 +2195,7 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2206,7 +2209,7 @@
         <v>267</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2220,7 +2223,7 @@
         <v>267</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2234,7 +2237,7 @@
         <v>267</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2248,7 +2251,7 @@
         <v>267</v>
       </c>
       <c r="D22" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2262,7 +2265,7 @@
         <v>267</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2276,7 +2279,7 @@
         <v>266</v>
       </c>
       <c r="D24" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2290,7 +2293,7 @@
         <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2304,7 +2307,7 @@
         <v>266</v>
       </c>
       <c r="D26" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2318,7 +2321,7 @@
         <v>266</v>
       </c>
       <c r="D27" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2332,7 +2335,7 @@
         <v>266</v>
       </c>
       <c r="D28" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2346,7 +2349,7 @@
         <v>266</v>
       </c>
       <c r="D29" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2360,7 +2363,7 @@
         <v>266</v>
       </c>
       <c r="D30" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2374,7 +2377,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2388,7 +2391,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2402,7 +2405,7 @@
         <v>266</v>
       </c>
       <c r="D33" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2416,7 +2419,7 @@
         <v>266</v>
       </c>
       <c r="D34" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2430,7 +2433,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2444,7 +2447,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2458,7 +2461,7 @@
         <v>267</v>
       </c>
       <c r="D37" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2472,7 +2475,7 @@
         <v>268</v>
       </c>
       <c r="D38" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2486,7 +2489,7 @@
         <v>268</v>
       </c>
       <c r="D39" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2500,7 +2503,7 @@
         <v>266</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2514,7 +2517,7 @@
         <v>266</v>
       </c>
       <c r="D41" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2528,7 +2531,7 @@
         <v>266</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2542,7 +2545,7 @@
         <v>266</v>
       </c>
       <c r="D43" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2556,7 +2559,7 @@
         <v>267</v>
       </c>
       <c r="D44" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2570,7 +2573,7 @@
         <v>266</v>
       </c>
       <c r="D45" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2584,7 +2587,7 @@
         <v>269</v>
       </c>
       <c r="D46" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2598,7 +2601,7 @@
         <v>267</v>
       </c>
       <c r="D47" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2612,7 +2615,7 @@
         <v>267</v>
       </c>
       <c r="D48" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2626,7 +2629,7 @@
         <v>267</v>
       </c>
       <c r="D49" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2640,7 +2643,7 @@
         <v>266</v>
       </c>
       <c r="D50" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2654,7 +2657,7 @@
         <v>266</v>
       </c>
       <c r="D51" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2668,7 +2671,7 @@
         <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2682,7 +2685,7 @@
         <v>266</v>
       </c>
       <c r="D53" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2696,7 +2699,7 @@
         <v>266</v>
       </c>
       <c r="D54" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2710,7 +2713,7 @@
         <v>266</v>
       </c>
       <c r="D55" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2724,7 +2727,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2738,7 +2741,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2752,7 +2755,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2766,7 +2769,7 @@
         <v>266</v>
       </c>
       <c r="D59" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2780,7 +2783,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2794,7 +2797,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2808,7 +2811,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2822,7 +2825,7 @@
         <v>268</v>
       </c>
       <c r="D63" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2836,7 +2839,7 @@
         <v>266</v>
       </c>
       <c r="D64" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2850,7 +2853,7 @@
         <v>266</v>
       </c>
       <c r="D65" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2864,7 +2867,7 @@
         <v>268</v>
       </c>
       <c r="D66" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2878,7 +2881,7 @@
         <v>266</v>
       </c>
       <c r="D67" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2892,7 +2895,7 @@
         <v>267</v>
       </c>
       <c r="D68" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2906,7 +2909,7 @@
         <v>267</v>
       </c>
       <c r="D69" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2920,7 +2923,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2934,7 +2937,7 @@
         <v>266</v>
       </c>
       <c r="D71" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2948,7 +2951,7 @@
         <v>266</v>
       </c>
       <c r="D72" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2962,7 +2965,7 @@
         <v>268</v>
       </c>
       <c r="D73" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2976,7 +2979,7 @@
         <v>268</v>
       </c>
       <c r="D74" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2990,7 +2993,7 @@
         <v>267</v>
       </c>
       <c r="D75" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3004,7 +3007,7 @@
         <v>268</v>
       </c>
       <c r="D76" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3018,7 +3021,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3032,7 +3035,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3046,7 +3049,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3060,7 +3063,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3074,7 +3077,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3088,7 +3091,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3102,7 +3105,7 @@
         <v>268</v>
       </c>
       <c r="D83" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3116,7 +3119,7 @@
         <v>268</v>
       </c>
       <c r="D84" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3130,7 +3133,7 @@
         <v>267</v>
       </c>
       <c r="D85" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3144,7 +3147,7 @@
         <v>268</v>
       </c>
       <c r="D86" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3158,7 +3161,7 @@
         <v>268</v>
       </c>
       <c r="D87" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3172,7 +3175,7 @@
         <v>267</v>
       </c>
       <c r="D88" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3186,7 +3189,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3200,7 +3203,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3214,7 +3217,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3228,7 +3231,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3242,7 +3245,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3256,7 +3259,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3270,7 +3273,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3284,7 +3287,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3298,7 +3301,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3312,7 +3315,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3326,7 +3329,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3340,7 +3343,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3354,7 +3357,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3368,7 +3371,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3382,7 +3385,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3396,7 +3399,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3410,7 +3413,7 @@
         <v>266</v>
       </c>
       <c r="D105" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3424,7 +3427,7 @@
         <v>266</v>
       </c>
       <c r="D106" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3438,7 +3441,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3452,7 +3455,7 @@
         <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3466,7 +3469,7 @@
         <v>267</v>
       </c>
       <c r="D109" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3480,7 +3483,7 @@
         <v>267</v>
       </c>
       <c r="D110" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3494,7 +3497,7 @@
         <v>267</v>
       </c>
       <c r="D111" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3508,7 +3511,7 @@
         <v>267</v>
       </c>
       <c r="D112" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3522,7 +3525,7 @@
         <v>267</v>
       </c>
       <c r="D113" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3536,7 +3539,7 @@
         <v>267</v>
       </c>
       <c r="D114" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3550,7 +3553,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3564,7 +3567,7 @@
         <v>266</v>
       </c>
       <c r="D116" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3578,7 +3581,7 @@
         <v>266</v>
       </c>
       <c r="D117" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3592,7 +3595,7 @@
         <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3606,7 +3609,7 @@
         <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3620,7 +3623,7 @@
         <v>268</v>
       </c>
       <c r="D120" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3634,7 +3637,7 @@
         <v>267</v>
       </c>
       <c r="D121" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3648,7 +3651,7 @@
         <v>267</v>
       </c>
       <c r="D122" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3662,7 +3665,7 @@
         <v>267</v>
       </c>
       <c r="D123" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3676,7 +3679,7 @@
         <v>267</v>
       </c>
       <c r="D124" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3690,7 +3693,7 @@
         <v>267</v>
       </c>
       <c r="D125" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3704,7 +3707,7 @@
         <v>267</v>
       </c>
       <c r="D126" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3718,7 +3721,7 @@
         <v>267</v>
       </c>
       <c r="D127" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3732,7 +3735,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3746,7 +3749,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3760,7 +3763,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3774,7 +3777,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3788,7 +3791,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3802,7 +3805,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3816,7 +3819,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3830,7 +3833,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3844,7 +3847,7 @@
         <v>268</v>
       </c>
       <c r="D136" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3858,7 +3861,7 @@
         <v>266</v>
       </c>
       <c r="D137" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3872,7 +3875,7 @@
         <v>266</v>
       </c>
       <c r="D138" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3886,7 +3889,7 @@
         <v>266</v>
       </c>
       <c r="D139" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3900,7 +3903,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3911,10 +3914,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D141" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3928,7 +3931,7 @@
         <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3939,10 +3942,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D143" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3956,7 +3959,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3970,7 +3973,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3984,7 +3987,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3998,7 +4001,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4012,7 +4015,7 @@
         <v>268</v>
       </c>
       <c r="D148" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4026,7 +4029,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4040,7 +4043,7 @@
         <v>267</v>
       </c>
       <c r="D150" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4054,7 +4057,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4068,7 +4071,7 @@
         <v>267</v>
       </c>
       <c r="D152" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4082,7 +4085,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4096,7 +4099,7 @@
         <v>266</v>
       </c>
       <c r="D154" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4110,7 +4113,7 @@
         <v>266</v>
       </c>
       <c r="D155" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4124,7 +4127,7 @@
         <v>266</v>
       </c>
       <c r="D156" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4138,7 +4141,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4152,7 +4155,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4166,7 +4169,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4180,7 +4183,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4194,7 +4197,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4208,7 +4211,7 @@
         <v>267</v>
       </c>
       <c r="D162" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4222,7 +4225,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4236,7 +4239,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4250,7 +4253,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4264,7 +4267,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4278,7 +4281,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4292,7 +4295,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4306,7 +4309,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4320,7 +4323,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4334,7 +4337,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4348,7 +4351,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4362,7 +4365,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4376,7 +4379,7 @@
         <v>267</v>
       </c>
       <c r="D174" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4390,7 +4393,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4404,7 +4407,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4418,7 +4421,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4432,7 +4435,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4446,7 +4449,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4460,7 +4463,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4474,7 +4477,7 @@
         <v>266</v>
       </c>
       <c r="D181" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4488,7 +4491,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4502,7 +4505,7 @@
         <v>266</v>
       </c>
       <c r="D183" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4516,7 +4519,7 @@
         <v>266</v>
       </c>
       <c r="D184" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4530,7 +4533,7 @@
         <v>266</v>
       </c>
       <c r="D185" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4544,7 +4547,7 @@
         <v>266</v>
       </c>
       <c r="D186" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4558,7 +4561,7 @@
         <v>266</v>
       </c>
       <c r="D187" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4572,7 +4575,7 @@
         <v>266</v>
       </c>
       <c r="D188" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4586,7 +4589,7 @@
         <v>266</v>
       </c>
       <c r="D189" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4600,7 +4603,7 @@
         <v>266</v>
       </c>
       <c r="D190" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4614,7 +4617,7 @@
         <v>266</v>
       </c>
       <c r="D191" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4625,10 +4628,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D192" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4642,7 +4645,7 @@
         <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4656,7 +4659,7 @@
         <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4670,7 +4673,7 @@
         <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4684,7 +4687,7 @@
         <v>266</v>
       </c>
       <c r="D196" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4698,7 +4701,7 @@
         <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4712,7 +4715,7 @@
         <v>267</v>
       </c>
       <c r="D198" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4726,7 +4729,7 @@
         <v>267</v>
       </c>
       <c r="D199" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4740,7 +4743,7 @@
         <v>267</v>
       </c>
       <c r="D200" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4754,7 +4757,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4768,7 +4771,7 @@
         <v>264</v>
       </c>
       <c r="D202" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4782,7 +4785,7 @@
         <v>267</v>
       </c>
       <c r="D203" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4796,7 +4799,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4810,7 +4813,7 @@
         <v>266</v>
       </c>
       <c r="D205" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4824,7 +4827,7 @@
         <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4838,7 +4841,7 @@
         <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4852,7 +4855,7 @@
         <v>266</v>
       </c>
       <c r="D208" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4866,7 +4869,7 @@
         <v>266</v>
       </c>
       <c r="D209" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4880,7 +4883,7 @@
         <v>266</v>
       </c>
       <c r="D210" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4894,7 +4897,7 @@
         <v>266</v>
       </c>
       <c r="D211" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4908,7 +4911,7 @@
         <v>266</v>
       </c>
       <c r="D212" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4922,7 +4925,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4936,7 +4939,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4950,7 +4953,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4964,7 +4967,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4978,7 +4981,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4992,7 +4995,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5006,7 +5009,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5020,7 +5023,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5034,7 +5037,7 @@
         <v>266</v>
       </c>
       <c r="D221" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5048,7 +5051,7 @@
         <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5062,7 +5065,7 @@
         <v>264</v>
       </c>
       <c r="D223" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5076,7 +5079,7 @@
         <v>266</v>
       </c>
       <c r="D224" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5090,7 +5093,7 @@
         <v>266</v>
       </c>
       <c r="D225" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5104,7 +5107,7 @@
         <v>266</v>
       </c>
       <c r="D226" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5118,7 +5121,7 @@
         <v>266</v>
       </c>
       <c r="D227" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5132,7 +5135,7 @@
         <v>266</v>
       </c>
       <c r="D228" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5146,7 +5149,7 @@
         <v>266</v>
       </c>
       <c r="D229" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5160,7 +5163,7 @@
         <v>266</v>
       </c>
       <c r="D230" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5174,7 +5177,7 @@
         <v>266</v>
       </c>
       <c r="D231" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5188,7 +5191,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5202,7 +5205,7 @@
         <v>266</v>
       </c>
       <c r="D233" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5216,7 +5219,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5230,7 +5233,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5244,7 +5247,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5258,7 +5261,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5272,7 +5275,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5286,7 +5289,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5300,7 +5303,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5314,7 +5317,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5328,7 +5331,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5342,7 +5345,7 @@
         <v>266</v>
       </c>
       <c r="D243" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5356,7 +5359,7 @@
         <v>266</v>
       </c>
       <c r="D244" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5370,7 +5373,7 @@
         <v>266</v>
       </c>
       <c r="D245" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5384,7 +5387,7 @@
         <v>266</v>
       </c>
       <c r="D246" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5398,7 +5401,7 @@
         <v>266</v>
       </c>
       <c r="D247" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5412,7 +5415,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5426,7 +5429,7 @@
         <v>266</v>
       </c>
       <c r="D249" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5440,7 +5443,7 @@
         <v>266</v>
       </c>
       <c r="D250" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5454,7 +5457,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5468,7 +5471,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5482,7 +5485,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5496,7 +5499,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5510,7 +5513,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5524,7 +5527,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
